--- a/output/pdf_financials_xlsx/MDK.P.xlsx
+++ b/output/pdf_financials_xlsx/MDK.P.xlsx
@@ -730,13 +730,13 @@
         <v>-0.035521</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.120645</v>
+        <v>-0.120645</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.05328</v>
+        <v>-0.05328</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.076141</v>
+        <v>-0.076141</v>
       </c>
     </row>
     <row r="17">
@@ -822,13 +822,13 @@
         <v>-0.035521</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.120645</v>
+        <v>-0.120645</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.05328</v>
+        <v>-0.05328</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.076141</v>
+        <v>-0.076141</v>
       </c>
     </row>
     <row r="21">
@@ -879,13 +879,13 @@
         <v>-0.035521</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.120645</v>
+        <v>-0.120645</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.05328</v>
+        <v>-0.05328</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.076141</v>
+        <v>-0.076141</v>
       </c>
     </row>
     <row r="24">
@@ -936,7 +936,7 @@
         <v>0.888025</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>-6.03225</v>
+        <v>6.03225</v>
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
@@ -959,13 +959,13 @@
         <v>-0.035521</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.120645</v>
+        <v>-0.120645</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.05328</v>
+        <v>-0.05328</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.076141</v>
+        <v>-0.076141</v>
       </c>
     </row>
     <row r="28">
@@ -997,13 +997,13 @@
         <v>-0.035521</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.120645</v>
+        <v>-0.120645</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.05328</v>
+        <v>-0.05328</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.076141</v>
+        <v>-0.076141</v>
       </c>
     </row>
     <row r="30">
@@ -1043,13 +1043,13 @@
         <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -2246,13 +2246,13 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.010949</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.010949</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.041193</v>
       </c>
     </row>
     <row r="93">
@@ -3410,7 +3410,11 @@
           <t>Reserve (Note 3)</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>-</t>
@@ -5082,10 +5086,10 @@
         </is>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.05328</v>
+        <v>-0.05328</v>
       </c>
       <c r="H56" s="5" t="n">
-        <v>0.076141</v>
+        <v>-0.076141</v>
       </c>
     </row>
     <row r="57">
@@ -5455,10 +5459,10 @@
         </is>
       </c>
       <c r="F67" s="5" t="n">
-        <v>0.120645</v>
+        <v>-0.120645</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>0.05328</v>
+        <v>-0.05328</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -5760,10 +5764,10 @@
         </is>
       </c>
       <c r="E76" s="5" t="n">
-        <v>0.035521</v>
+        <v>-0.035521</v>
       </c>
       <c r="F76" s="5" t="n">
-        <v>0.120645</v>
+        <v>-0.120645</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/MDK.P.xlsx
+++ b/output/pdf_financials_xlsx/MDK.P.xlsx
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.20036</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0.213995</v>
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.20036</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0.213995</v>
@@ -3656,7 +3656,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E16" s="5" t="n">

--- a/output/pdf_financials_xlsx/MDK.P.xlsx
+++ b/output/pdf_financials_xlsx/MDK.P.xlsx
@@ -5036,7 +5036,11 @@
           <t>Interest revenue</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>InterestIncome</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
           <t>-</t>
